--- a/output/pdf_financials_xlsx/AFF.xlsx
+++ b/output/pdf_financials_xlsx/AFF.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.770769</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.860109</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.020493</v>
       </c>
     </row>
     <row r="93">
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0144</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.020447</v>
+        <v>0.006047</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.019405</v>
       </c>
     </row>
     <row r="119">
@@ -3104,7 +3104,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>3.770769</v>
       </c>
@@ -3540,7 +3544,11 @@
           <t>Exploration and Evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.0144</v>
       </c>

--- a/output/pdf_financials_xlsx/AFF.xlsx
+++ b/output/pdf_financials_xlsx/AFF.xlsx
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000495</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006972</v>
       </c>
     </row>
     <row r="102">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.325236</v>
+        <v>0.325731</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.443696</v>
+        <v>0.44372</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.036448</v>
+        <v>-0.04342</v>
       </c>
     </row>
     <row r="107">
@@ -3420,7 +3420,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.000495</v>
       </c>
